--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R84cd2bdf74ff4954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb9fd40efb1bc426d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb9fd40efb1bc426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45386f6400bb4292"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45386f6400bb4292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9054f349de5147cc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9054f349de5147cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5af0ca27d8f24307"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5af0ca27d8f24307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd2fa5b2cd6564324"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd2fa5b2cd6564324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e8778ae12d14784"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e8778ae12d14784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R133c2c07f1094653"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R133c2c07f1094653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R704a316f61aa44b5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R704a316f61aa44b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3133cedaf030450b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3133cedaf030450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95f5b907d1c54ae7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95f5b907d1c54ae7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R028b9935b7284c7f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R028b9935b7284c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ff84fdc36ca495e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ff84fdc36ca495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63915bc31b9d44b0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63915bc31b9d44b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R118705e162a24d10"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R118705e162a24d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb2c6ab6fe9924580"/>
   </x:sheets>
 </x:workbook>
 </file>
